--- a/output/reciprocal_deposits_q2_2026.xlsx
+++ b/output/reciprocal_deposits_q2_2026.xlsx
@@ -13775,7 +13775,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Firms excluded, not required, or not yet filed</t>
+          <t>Disclosures not retrievable by an automated client</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
